--- a/Docs/游戏配置/英雄与技能配置.xlsx
+++ b/Docs/游戏配置/英雄与技能配置.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ID查询" sheetId="1" r:id="R801d048be2c54429"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄" sheetId="2" r:id="Rb666076d90574a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能" sheetId="3" r:id="Rf529aaf5d58f4ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物" sheetId="4" r:id="R7d47de1883514e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄技能装配" sheetId="5" r:id="R6caea46a1c964e2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能阶段" sheetId="6" r:id="Rbc1075b38a384842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ID查询" sheetId="1" r:id="Rabcdc716f5134ba6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄" sheetId="2" r:id="R6862f185cd194444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能" sheetId="3" r:id="R5b1157b52bcc47e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物" sheetId="4" r:id="R9f7606aa31954d1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄技能装配" sheetId="5" r:id="R9492d8b79a674f78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能阶段" sheetId="6" r:id="Ra81db35aceea4f07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -151,7 +151,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -162,7 +162,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -497,7 +497,7 @@
         <x:v>快照日期</x:v>
       </x:c>
       <x:c r="B3" s="1" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-10-22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
@@ -554,7 +554,7 @@
       </x:c>
       <x:c r="B10" s="18" t="str">
         <x:f>IF(B6&lt;&gt;1,"请检查输入或重复ID",IF(B7="英雄",INDEX('英雄'!$I$6:$I$1005,MATCH(B4,'英雄'!$A$6:$A$1005,0)),IF(B7="技能",INDEX('技能'!$N$6:$N$1005,MATCH(B4,'技能'!$A$6:$A$1005,0)),INDEX('怪物'!$I$6:$I$1005,MATCH(B4,'怪物'!$A$6:$A$1005,0)))))</x:f>
-        <x:v>Assets/Game/Skills/Foundation/Skills/冰晶巨箭.asset</x:v>
+        <x:v>Assets/GameData/技能/1003_冰晶巨箭.asset</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
@@ -696,7 +696,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>源自已保存的 Unity 配置，2026-09-28。蓝字为可编辑数据，灰底为计算检查。</x:v>
+        <x:v>源自已保存的 Unity 配置，2026-10-22；Excel 是快照，修改 GameData 后重新导出。</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -793,7 +793,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Assets/Game/Skills/Foundation/寒冰射手.asset</x:v>
+        <x:v>Assets/GameData/英雄/2000_寒冰射手.asset</x:v>
       </x:c>
       <x:c r="J6" s="13" t="str">
         <x:f>IF(A6="","缺少ID",IF(NOT(ISNUMBER(A6)),"需数字整数",IF(NOT(AND(ISNUMBER(A6),A6&gt;=2000,A6&lt;=2999,MOD(A6,1)=0)),"编号越界或非整数",IF(COUNTIFS('英雄'!$A$6:$A$1005,A6)+COUNTIFS('技能'!$A$6:$A$1005,A6)+COUNTIFS('怪物'!$A$6:$A$1005,A6)=1,"唯一","ID重复"))))</x:f>
@@ -826,7 +826,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>Assets/Game/Skills/Foundation/寒冰射手·换槽示例.asset</x:v>
+        <x:v>Assets/GameData/编辑示例/换槽/2001_寒冰射手·换槽示例.asset</x:v>
       </x:c>
       <x:c r="J7" s="13" t="str">
         <x:f>IF(A7="","缺少ID",IF(NOT(ISNUMBER(A7)),"需数字整数",IF(NOT(AND(ISNUMBER(A7),A7&gt;=2000,A7&lt;=2999,MOD(A7,1)=0)),"编号越界或非整数",IF(COUNTIFS('英雄'!$A$6:$A$1005,A7)+COUNTIFS('技能'!$A$6:$A$1005,A7)+COUNTIFS('怪物'!$A$6:$A$1005,A7)=1,"唯一","ID重复"))))</x:f>
@@ -845,7 +845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea8a6f579a00460b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbd1fd8bc8914819"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -896,7 +896,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>源自已保存的 Unity 配置，2026-09-28。蓝字为可编辑数据，灰底为计算检查。</x:v>
+        <x:v>源自已保存的 Unity 配置，2026-10-22；Excel 是快照，修改 GameData 后重新导出。</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -1028,7 +1028,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="10" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
         <x:v>0</x:v>
@@ -1037,7 +1037,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
         <x:v>1</x:v>
@@ -1052,7 +1052,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N6" s="12" t="str">
-        <x:v>Assets/Game/Skills/Foundation/Skills/冰霜专注.asset</x:v>
+        <x:v>Assets/GameData/技能/1000_冰霜专注.asset</x:v>
       </x:c>
       <x:c r="O6" s="12"/>
       <x:c r="P6" s="12"/>
@@ -1078,7 +1078,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
         <x:v>0</x:v>
@@ -1087,7 +1087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
         <x:v>1</x:v>
@@ -1102,7 +1102,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N7" s="12" t="str">
-        <x:v>Assets/Game/Skills/Foundation/Skills/冰霜扇击.asset</x:v>
+        <x:v>Assets/GameData/技能/1001_冰霜扇击.asset</x:v>
       </x:c>
       <x:c r="O7" s="12"/>
       <x:c r="P7" s="12"/>
@@ -1137,13 +1137,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K8" s="10" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="11" t="n">
         <x:v>0</x:v>
@@ -1152,7 +1152,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N8" s="12" t="str">
-        <x:v>Assets/Game/Skills/Foundation/Skills/冰霜冲击.asset</x:v>
+        <x:v>Assets/GameData/技能/1002_冰霜冲击.asset</x:v>
       </x:c>
       <x:c r="O8" s="12"/>
       <x:c r="P8" s="12"/>
@@ -1178,7 +1178,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="F9" s="10" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
         <x:v>0</x:v>
@@ -1187,7 +1187,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J9" s="11" t="n">
         <x:v>1</x:v>
@@ -1202,7 +1202,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N9" s="12" t="str">
-        <x:v>Assets/Game/Skills/Foundation/Skills/冰晶巨箭.asset</x:v>
+        <x:v>Assets/GameData/技能/1003_冰晶巨箭.asset</x:v>
       </x:c>
       <x:c r="O9" s="12"/>
       <x:c r="P9" s="12"/>
@@ -1252,7 +1252,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="12" t="str">
-        <x:v>Assets/Game/Abilities/Settings/E Inspire.asset</x:v>
+        <x:v>Assets/GameData/历史示例/技能系统/1004_E_鼓舞示例.asset</x:v>
       </x:c>
       <x:c r="O10" s="12" t="str">
         <x:v>自身圆形</x:v>
@@ -1306,7 +1306,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N11" s="12" t="str">
-        <x:v>Assets/Game/Abilities/Settings/Q Burst.asset</x:v>
+        <x:v>Assets/GameData/历史示例/技能系统/1005_Q_爆发示例.asset</x:v>
       </x:c>
       <x:c r="O11" s="12" t="str">
         <x:v>即时圆形</x:v>
@@ -1360,7 +1360,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="12" t="str">
-        <x:v>Assets/Game/Abilities/Settings/W Frost Field.asset</x:v>
+        <x:v>Assets/GameData/历史示例/技能系统/1006_W_冰霜区域示例.asset</x:v>
       </x:c>
       <x:c r="O12" s="12" t="str">
         <x:v>持续圆形</x:v>
@@ -1414,7 +1414,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N13" s="12" t="str">
-        <x:v>Assets/Game/SkillAuthoring/Content/范围技能示例.asset</x:v>
+        <x:v>Assets/GameData/编辑示例/技能工作台/1007_范围技能示例.asset</x:v>
       </x:c>
       <x:c r="O13" s="12"/>
       <x:c r="P13" s="12"/>
@@ -1435,7 +1435,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b4e08990aa64cd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc17b217b442541f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1472,7 +1472,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>源自已保存的 Unity 配置，2026-09-28。蓝字为可编辑数据，灰底为计算检查。</x:v>
+        <x:v>源自已保存的 Unity 配置，2026-10-22；Excel 是快照，修改 GameData 后重新导出。</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -1588,7 +1588,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf038cdd3036427b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9674eac63d644411"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1619,7 +1619,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>源自已保存的 Unity 配置，2026-09-28。蓝字为可编辑数据，灰底为计算检查。</x:v>
+        <x:v>源自已保存的 Unity 配置，2026-10-22；Excel 是快照，修改 GameData 后重新导出。</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -1880,7 +1880,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re97d58f0b0c14447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00294d4836cb4509"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1937,7 +1937,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>源自已保存的 Unity 配置，2026-09-28。蓝字为可编辑数据，灰底为计算检查。</x:v>
+        <x:v>源自已保存的 Unity 配置，2026-10-22；Excel 是快照，修改 GameData 后重新导出。</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -2132,8 +2132,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S6" s="12" t="str">
-        <x:v>范围技能示例·伤害效果 10
-范围技能示例·伤害效果 10</x:v>
+        <x:v>4000 · 4000_范围技能示例·伤害效果：{"configId":4000,"stableId":"effect.9461525a7492404b8e18bf95738f6069","target":0,"amount":10.0}
+4000 · 4000_范围技能示例·伤害效果：{"configId":4000,"stableId":"effect.9461525a7492404b8e18bf95738f6069","target":0,"amount":10.0}</x:v>
       </x:c>
       <x:c r="T6" s="12" t="str"/>
     </x:row>
@@ -2193,12 +2193,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S7" s="12" t="str">
-        <x:v>冰晶爆炸伤害 16
-施加冰晶减速（buff.crystal_slow，强度 1，持续 3 秒）</x:v>
+        <x:v>4001 · 4001_冰晶爆炸伤害：{"configId":4001,"stableId":"effect.ca77a76ab9b249219c00753aa078a9fa","target":0,"amount":100.0}
+4005 · 4005_施加冰晶减速：{"configId":4005,"stableId":"effect.ee1720bbecfa4fae88de5169e8239271","target":0,"buff":{"instanceID":56234},"buffScale":1.0}；{"configId":5005,"stableId":"buff.crystal_slow","displayName":"冰晶减速","duration":3.0,"interval":1.0,"periodicDamage":0.0,"stacking":0,"maxStacks":1,"dispellable":true,"sourcePolicy":1,"modifiers":[{"attribute":0,"operation":1,"value":-0.5}],"controls":0,"moveSpeedPercent":0.0,"attackDamageFlat":0.0,"healthRegen":0.0}</x:v>
       </x:c>
       <x:c r="T7" s="12" t="str">
-        <x:v>冰晶首中伤害 20
-施加冰晶眩晕（buff.crystal_stun，强度 1，持续 1.5 秒）</x:v>
+        <x:v>4002 · 4002_冰晶首中伤害：{"configId":4002,"stableId":"effect.6653cd78205341239d33d86fb47d7fb4","target":0,"amount":120.0}
+4006 · 4006_施加冰晶眩晕：{"configId":4006,"stableId":"effect.645fd12511cd440483f47d5e53c58c3b","target":0,"buff":{"instanceID":56588},"buffScale":1.0}；{"configId":5006,"stableId":"buff.crystal_stun","displayName":"冰晶眩晕","duration":1.5,"interval":1.0,"periodicDamage":0.0,"stacking":0,"maxStacks":1,"dispellable":true,"sourcePolicy":1,"modifiers":[],"controls":7,"moveSpeedPercent":0.0,"attackDamageFlat":0.0,"healthRegen":0.0}</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S8" s="12" t="str">
-        <x:v>施加冰霜专注（buff.frost_focus，强度 1，持续 5 秒）</x:v>
+        <x:v>4007 · 4007_施加冰霜专注：{"configId":4007,"stableId":"effect.44ed1aebdd5e4de0a989f3007cad7861","target":0,"buff":{"instanceID":56684},"buffScale":1.0}；{"configId":5007,"stableId":"buff.frost_focus","displayName":"冰霜专注","duration":5.0,"interval":1.0,"periodicDamage":0.0,"stacking":0,"maxStacks":1,"dispellable":true,"sourcePolicy":1,"modifiers":[{"attribute":2,"operation":1,"value":0.6000000238418579}],"controls":0,"moveSpeedPercent":0.0,"attackDamageFlat":0.0,"healthRegen":0.0}</x:v>
       </x:c>
       <x:c r="T8" s="12" t="str"/>
     </x:row>
@@ -2317,7 +2317,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S9" s="12" t="str">
-        <x:v>冰霜冲击伤害 18</x:v>
+        <x:v>4003 · 4003_冰霜冲击伤害：{"configId":4003,"stableId":"effect.47fd7946cfdb4f80843f46b888106ee2","target":0,"amount":90.0}</x:v>
       </x:c>
       <x:c r="T9" s="12" t="str"/>
     </x:row>
@@ -2377,15 +2377,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S10" s="12" t="str">
-        <x:v>冰霜扇击伤害 30
-施加扇击减速（buff.volley_slow，强度 1，持续 2.5 秒）</x:v>
+        <x:v>4004 · 4004_冰霜扇击伤害：{"configId":4004,"stableId":"effect.5b2e0dd30abb4011a84f06b01bfe4979","target":0,"amount":60.0}
+4008 · 4008_施加扇击减速：{"configId":4008,"stableId":"effect.a982e694958845c1bd2af1b286dbaac6","target":0,"buff":{"instanceID":56068},"buffScale":1.0}；{"configId":5008,"stableId":"buff.volley_slow","displayName":"扇击减速","duration":2.5,"interval":1.0,"periodicDamage":0.0,"stacking":0,"maxStacks":1,"dispellable":true,"sourcePolicy":1,"modifiers":[{"attribute":0,"operation":1,"value":-0.3499999940395355}],"controls":0,"moveSpeedPercent":0.0,"attackDamageFlat":0.0,"healthRegen":0.0}</x:v>
       </x:c>
       <x:c r="T10" s="12" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b57559445ef4dc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7c98ecf283047f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Docs/游戏配置/英雄与技能配置.xlsx
+++ b/Docs/游戏配置/英雄与技能配置.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ID查询" sheetId="1" r:id="Rabcdc716f5134ba6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄" sheetId="2" r:id="R6862f185cd194444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能" sheetId="3" r:id="R5b1157b52bcc47e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物" sheetId="4" r:id="R9f7606aa31954d1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄技能装配" sheetId="5" r:id="R9492d8b79a674f78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能阶段" sheetId="6" r:id="Ra81db35aceea4f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ID查询" sheetId="1" r:id="Rec242373f3df4bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄" sheetId="2" r:id="R56a5573efccb4c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能" sheetId="3" r:id="R5e22f52ff70b4cb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物" sheetId="4" r:id="Rbede2684a85346cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄技能装配" sheetId="5" r:id="Ra270f18e1ea64616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能阶段" sheetId="6" r:id="Rac19fb5d57b04537"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -778,7 +778,7 @@
         <x:v>正式配置</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>300</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
         <x:v>10</x:v>
@@ -811,7 +811,7 @@
         <x:v>换槽示例</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>300</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E7" s="10" t="n">
         <x:v>10</x:v>
@@ -845,7 +845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbd1fd8bc8914819"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0095762e1c7e4d55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1037,7 +1037,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
         <x:v>1</x:v>
@@ -1087,7 +1087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
         <x:v>1</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
         <x:v>2</x:v>
@@ -1187,7 +1187,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J9" s="11" t="n">
         <x:v>1</x:v>
@@ -1435,7 +1435,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc17b217b442541f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25e787b7325c45f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1588,7 +1588,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9674eac63d644411"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0975ce039e6c4043"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1880,7 +1880,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00294d4836cb4509"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0febabe5ec654b68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2385,7 +2385,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7c98ecf283047f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cd8a57adc1141c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>